--- a/面试/面试公司榜.xlsx
+++ b/面试/面试公司榜.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="14175"/>
+    <workbookView windowWidth="27945" windowHeight="14175" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="外包公司黑名单" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
   <si>
     <t>公司名称</t>
   </si>
@@ -64,6 +64,12 @@
   </si>
   <si>
     <t>app违规扣费，网上一堆用户投诉其乱收费、广告多、虚假宣传、不给提现，了解的人越来越多，对其盈利能力肯定会有影响，打工人的工资有没有保证都是问题</t>
+  </si>
+  <si>
+    <t>杭州笛佛软件/吉客云</t>
+  </si>
+  <si>
+    <t>公司一开始提上市，大量招人，七月份招聘90人，七月亏损以后，借考核不达标八月份辞退将近70人，我们都是校招来的，一定会好好给贵公司宣传一番，各种骚操作，为了重新分组还提前考核掉一批，真伤应届生的心</t>
   </si>
 </sst>
 </file>
@@ -1248,7 +1254,14 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1"/>
+    <row r="5" ht="20" customHeight="1" spans="1:2">
+      <c r="A5" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" t="s">
+        <v>13</v>
+      </c>
+    </row>
     <row r="6" ht="20" customHeight="1"/>
     <row r="7" ht="20" customHeight="1"/>
     <row r="8" ht="20" customHeight="1"/>

--- a/面试/面试公司榜.xlsx
+++ b/面试/面试公司榜.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="14175" activeTab="1"/>
+    <workbookView windowWidth="27945" windowHeight="14175"/>
   </bookViews>
   <sheets>
     <sheet name="外包公司黑名单" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
   <si>
     <t>公司名称</t>
   </si>
@@ -46,6 +46,12 @@
   </si>
   <si>
     <t xml:space="preserve">神州数码不是外包，但是神州信息是子公司，属于外包业务，不给你报销 </t>
+  </si>
+  <si>
+    <t>博彦科技公司</t>
+  </si>
+  <si>
+    <t>接到offer，毁约，被列入北京黑名单系统</t>
   </si>
   <si>
     <t>深睿医疗</t>
@@ -1041,7 +1047,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1"/>
+    <row r="4" ht="20" customHeight="1" spans="1:2">
+      <c r="A4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+    </row>
     <row r="5" ht="20" customHeight="1"/>
     <row r="6" ht="20" customHeight="1"/>
     <row r="7" ht="20" customHeight="1"/>
@@ -1232,34 +1245,34 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:2">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B2" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2">
       <c r="A3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1"/>

--- a/面试/面试公司榜.xlsx
+++ b/面试/面试公司榜.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
   <si>
     <t>公司名称</t>
   </si>
@@ -52,6 +52,12 @@
   </si>
   <si>
     <t>接到offer，毁约，被列入北京黑名单系统</t>
+  </si>
+  <si>
+    <t>江苏谷科软件有限公司</t>
+  </si>
+  <si>
+    <t>长亮科技</t>
   </si>
   <si>
     <t>深睿医疗</t>
@@ -1055,8 +1061,16 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1"/>
-    <row r="6" ht="20" customHeight="1"/>
+    <row r="5" ht="20" customHeight="1" spans="1:2">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:2">
+      <c r="A6" t="s">
+        <v>9</v>
+      </c>
+    </row>
     <row r="7" ht="20" customHeight="1"/>
     <row r="8" ht="20" customHeight="1"/>
     <row r="9" ht="20" customHeight="1"/>
@@ -1245,34 +1259,34 @@
     </row>
     <row r="2" ht="20" customHeight="1" spans="1:2">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:2">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:2">
       <c r="A4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:2">
       <c r="A5" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B5" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1"/>
